--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/XRF/Panel 02/front/xrf_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/XRF/Panel 02/front/xrf_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.73598</v>
+        <v>17.53246</v>
       </c>
       <c r="D2" t="n">
-        <v>16.86408</v>
+        <v>17.05003</v>
       </c>
       <c r="E2" t="n">
-        <v>16.77168</v>
+        <v>17.09701</v>
       </c>
       <c r="F2" t="n">
-        <v>42.58796</v>
+        <v>43.16643</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05189</v>
+        <v>0.05221</v>
       </c>
       <c r="H2" t="n">
-        <v>1.83087</v>
+        <v>1.84247</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.18768</v>
+        <v>17.30348</v>
       </c>
       <c r="D3" t="n">
-        <v>16.91506</v>
+        <v>16.74841</v>
       </c>
       <c r="E3" t="n">
-        <v>17.1825</v>
+        <v>17.10317</v>
       </c>
       <c r="F3" t="n">
-        <v>42.98525</v>
+        <v>43.58437</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05174</v>
+        <v>0.05163</v>
       </c>
       <c r="H3" t="n">
-        <v>1.87292</v>
+        <v>1.83187</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.05596</v>
+        <v>17.17564</v>
       </c>
       <c r="D4" t="n">
-        <v>17.14289</v>
+        <v>16.79472</v>
       </c>
       <c r="E4" t="n">
-        <v>16.95005</v>
+        <v>16.95965</v>
       </c>
       <c r="F4" t="n">
-        <v>43.37937</v>
+        <v>42.67284</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05177</v>
+        <v>0.05148</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83817</v>
+        <v>1.88776</v>
       </c>
     </row>
   </sheetData>
